--- a/parameters/UA/hydrogen/demand_parameters.xlsx
+++ b/parameters/UA/hydrogen/demand_parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\engs2859\Desktop\Geo-X\Geo-X\parameters\UA\hydrogen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010BECBA-804C-4F5D-B0CB-0F651609D4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14108EEA-F5FC-4BFC-9E4A-3332C47324E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3030" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{1EFB3969-2EEE-7045-9FD0-00480E0E3DAF}"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{1EFB3969-2EEE-7045-9FD0-00480E0E3DAF}"/>
   </bookViews>
   <sheets>
     <sheet name="Demand centers" sheetId="2" r:id="rId1"/>
@@ -55,7 +55,7 @@
     <t>Demand state</t>
   </si>
   <si>
-    <t>Kyiv</t>
+    <t>Zakarpattia</t>
   </si>
 </sst>
 </file>
@@ -111,10 +111,9 @@
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
@@ -444,36 +443,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3">
-        <v>50.42</v>
-      </c>
-      <c r="C2" s="3">
-        <v>30.58</v>
-      </c>
-      <c r="D2" s="2">
+      <c r="B2" s="2">
+        <v>48.6</v>
+      </c>
+      <c r="C2" s="2">
+        <v>22.3</v>
+      </c>
+      <c r="D2">
         <v>10000000</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>1</v>
       </c>
     </row>
